--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file HOSPITAL LOCATION (44.1)</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the source HOSPITAL LOCATION (44.1)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation441.xlsx
+++ b/docs/StructureDefinition-HospitalLocation441.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
